--- a/Unity/Assets/Config/Excel/AIConfig.xlsx
+++ b/Unity/Assets/Config/Excel/AIConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12795" tabRatio="809"/>
+    <workbookView windowWidth="27945" windowHeight="12795" tabRatio="809"/>
   </bookViews>
   <sheets>
     <sheet name="AIConfig_1" sheetId="6" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>##var</t>
   </si>
@@ -72,18 +72,6 @@
   </si>
   <si>
     <t>节点参数</t>
-  </si>
-  <si>
-    <t>AI_XunLuo</t>
-  </si>
-  <si>
-    <t>巡逻</t>
-  </si>
-  <si>
-    <t>AI_Retreat</t>
-  </si>
-  <si>
-    <t>撤退</t>
   </si>
   <si>
     <t>AI_ZhuiJi</t>
@@ -1057,8 +1045,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.625" style="1" customWidth="1"/>
@@ -1171,40 +1159,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" ht="16.5" spans="2:6">
-      <c r="B6" s="2">
-        <v>103</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2">
-        <v>3</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="2:6">
-      <c r="B7" s="2">
-        <v>104</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2">
-        <v>4</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/AIConfig.xlsx
+++ b/Unity/Assets/Config/Excel/AIConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -74,16 +74,22 @@
     <t>节点参数</t>
   </si>
   <si>
+    <t>AI_Follow</t>
+  </si>
+  <si>
+    <t>跟随</t>
+  </si>
+  <si>
+    <t>AI_Attack</t>
+  </si>
+  <si>
+    <t>攻击</t>
+  </si>
+  <si>
     <t>AI_ZhuiJi</t>
   </si>
   <si>
     <t>追击</t>
-  </si>
-  <si>
-    <t>AI_Attack</t>
-  </si>
-  <si>
-    <t>攻击</t>
   </si>
 </sst>
 </file>
@@ -1045,8 +1051,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="6"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.625" style="1" customWidth="1"/>
@@ -1159,6 +1165,40 @@
         <v>18</v>
       </c>
     </row>
+    <row r="6" ht="16.5" spans="2:6">
+      <c r="B6" s="2">
+        <v>201</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="2:6">
+      <c r="B7" s="2">
+        <v>202</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Unity/Assets/Config/Excel/AIConfig.xlsx
+++ b/Unity/Assets/Config/Excel/AIConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -80,16 +80,16 @@
     <t>跟随</t>
   </si>
   <si>
+    <t>AI_ZhuiJi</t>
+  </si>
+  <si>
+    <t>追击</t>
+  </si>
+  <si>
     <t>AI_Attack</t>
   </si>
   <si>
     <t>攻击</t>
-  </si>
-  <si>
-    <t>AI_ZhuiJi</t>
-  </si>
-  <si>
-    <t>追击</t>
   </si>
 </sst>
 </file>
@@ -1051,8 +1051,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="9.625" style="1" customWidth="1"/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="6" ht="16.5" spans="2:6">
       <c r="B6" s="2">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>19</v>
@@ -1184,19 +1184,36 @@
     </row>
     <row r="7" ht="16.5" spans="2:6">
       <c r="B7" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="2:6">
+      <c r="B8" s="2">
+        <v>202</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
